--- a/app/templates/schet-shablon.xlsx
+++ b/app/templates/schet-shablon.xlsx
@@ -11,127 +11,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+  <si>
+    <t>{{bank_name}}</t>
+  </si>
+  <si>
+    <t>БИК</t>
+  </si>
+  <si>
+    <t>{{bik}}</t>
+  </si>
+  <si>
+    <t>Сч. №</t>
+  </si>
+  <si>
+    <t>{{cor_account}}</t>
+  </si>
+  <si>
+    <t>Банк получателя</t>
+  </si>
+  <si>
+    <t>ИНН</t>
+  </si>
+  <si>
+    <t>{{inn}}</t>
+  </si>
+  <si>
+    <t>КПП</t>
+  </si>
+  <si>
+    <t>{{kpp}}</t>
+  </si>
+  <si>
+    <t>{{account}}</t>
+  </si>
+  <si>
+    <t>{{recipient}}</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Получатель</t>
+  </si>
+  <si>
+    <t>Счет на оплату № {{invoice_number}} от {{invoice_date}}</t>
+  </si>
+  <si>
+    <t>Поставщик:</t>
+  </si>
+  <si>
+    <t>{{supplier_info}}</t>
+  </si>
+  <si>
+    <t>Покупатель:</t>
+  </si>
+  <si>
+    <t>{{customer_info}}</t>
+  </si>
+  <si>
+    <t>Основание:</t>
+  </si>
+  <si>
+    <t>{{foundation}}</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Наименование товара, работ, услуг</t>
+  </si>
+  <si>
+    <t>Кол-во</t>
+  </si>
+  <si>
+    <t>Ед. изм.</t>
+  </si>
+  <si>
+    <t>Цена</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>{{item_number}}</t>
+  </si>
+  <si>
+    <t>{{item_name}}</t>
+  </si>
+  <si>
+    <t>{{item_quantity}}</t>
+  </si>
+  <si>
+    <t>{{item_unit}}</t>
+  </si>
+  <si>
+    <t>{{item_price}}</t>
+  </si>
+  <si>
+    <t>{{item_sum}}</t>
+  </si>
+  <si>
+    <t>Итого:</t>
+  </si>
+  <si>
+    <t>{{total_sum}}</t>
+  </si>
+  <si>
+    <t>{{nds_title}}</t>
+  </si>
+  <si>
+    <t>{{total_vat}}</t>
+  </si>
+  <si>
+    <t>Всего к оплате:</t>
+  </si>
+  <si>
+    <t>{{total_to_pay}}</t>
+  </si>
+  <si>
+    <t>Всего наименований {{total_items_count}}, на сумму {{total_to_pay}} руб.</t>
+  </si>
+  <si>
+    <t>{{total_sum_text}}</t>
+  </si>
   <si>
     <t>{{head_warning}}</t>
-  </si>
-  <si>
-    <t>{{bank_name}}</t>
-  </si>
-  <si>
-    <t>БИК</t>
-  </si>
-  <si>
-    <t>{{bik}}</t>
-  </si>
-  <si>
-    <t>Сч. №</t>
-  </si>
-  <si>
-    <t>{{cor_account}}</t>
-  </si>
-  <si>
-    <t>Банк получателя</t>
-  </si>
-  <si>
-    <t>ИНН</t>
-  </si>
-  <si>
-    <t>{{inn}}</t>
-  </si>
-  <si>
-    <t>КПП</t>
-  </si>
-  <si>
-    <t>{{kpp}}</t>
-  </si>
-  <si>
-    <t>{{account}}</t>
-  </si>
-  <si>
-    <t>{{recipient}}</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Получатель</t>
-  </si>
-  <si>
-    <t>Счет на оплату № {{invoice_number}} от {{invoice_date}}</t>
-  </si>
-  <si>
-    <t>Поставщик:</t>
-  </si>
-  <si>
-    <t>{{supplier_info}}</t>
-  </si>
-  <si>
-    <t>Покупатель:</t>
-  </si>
-  <si>
-    <t>{{customer_info}}</t>
-  </si>
-  <si>
-    <t>№</t>
-  </si>
-  <si>
-    <t>Наименование товара, работ, услуг</t>
-  </si>
-  <si>
-    <t>Коли-
-чество</t>
-  </si>
-  <si>
-    <t>Ед. изм.</t>
-  </si>
-  <si>
-    <t>Цена</t>
-  </si>
-  <si>
-    <t>Сумма</t>
-  </si>
-  <si>
-    <t>{{item_number}}</t>
-  </si>
-  <si>
-    <t>{{item_name}}</t>
-  </si>
-  <si>
-    <t>{{item_quantity}}</t>
-  </si>
-  <si>
-    <t>{{item_unit}}</t>
-  </si>
-  <si>
-    <t>{{item_price}}</t>
-  </si>
-  <si>
-    <t>{{item_sum}}</t>
-  </si>
-  <si>
-    <t>Итого:</t>
-  </si>
-  <si>
-    <t>{{total_sum}}</t>
-  </si>
-  <si>
-    <t>{{nds_title}}</t>
-  </si>
-  <si>
-    <t>{{total_vat}}</t>
-  </si>
-  <si>
-    <t>Всего к оплате:</t>
-  </si>
-  <si>
-    <t>{{total_to_pay}}</t>
-  </si>
-  <si>
-    <t>Всего наименований {{total_items_count}}, на сумму {{total_to_pay}} рублей 00 копеек</t>
-  </si>
-  <si>
-    <t>{{total_sum_text}}</t>
   </si>
   <si>
     <t>Руководитель</t>
@@ -150,7 +155,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -159,11 +164,6 @@
     </font>
     <font>
       <sz val="8.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="7.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -204,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border/>
     <border>
       <left/>
@@ -401,6 +401,11 @@
       </bottom>
     </border>
     <border>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -545,47 +550,47 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="21" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="23" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="24" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -598,30 +603,37 @@
     <xf borderId="14" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="26" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="28" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="29" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="30" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="31" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="32" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="32" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="30" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="34" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="35" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="34" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="35" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="36" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -639,41 +651,44 @@
     <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="36" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="37" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="37" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="38" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="38" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="39" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="39" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="41" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="37" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="38" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="41" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="42" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -908,13 +923,11 @@
     <col customWidth="1" min="18" max="18" width="0.38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1">
+    <row r="1" ht="24.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="D1" s="2"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -931,7 +944,7 @@
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -944,11 +957,11 @@
       <c r="J2" s="5"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
@@ -958,11 +971,11 @@
       <c r="A3" s="12"/>
       <c r="K3" s="13"/>
       <c r="L3" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
@@ -970,7 +983,7 @@
     </row>
     <row r="4" ht="7.5" customHeight="1">
       <c r="A4" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -991,30 +1004,30 @@
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
       <c r="F5" s="8"/>
       <c r="G5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="24" t="s">
         <v>9</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>10</v>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
       <c r="K5" s="8"/>
       <c r="L5" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
@@ -1022,7 +1035,7 @@
     </row>
     <row r="6" ht="27.75" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -1035,11 +1048,11 @@
       <c r="J6" s="10"/>
       <c r="K6" s="11"/>
       <c r="L6" s="27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M6" s="16"/>
       <c r="N6" s="27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
@@ -1047,7 +1060,7 @@
     </row>
     <row r="7" ht="7.5" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1087,7 +1100,7 @@
     </row>
     <row r="9" ht="27.75" customHeight="1">
       <c r="A9" s="28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
@@ -1125,15 +1138,15 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" ht="12.0" customHeight="1">
+    <row r="11" ht="31.5" customHeight="1">
       <c r="A11" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -1167,15 +1180,15 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" ht="12.0" customHeight="1">
+    <row r="13" ht="30.0" customHeight="1">
       <c r="A13" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -1190,116 +1203,120 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" ht="6.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="A14" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="33"/>
     </row>
     <row r="15" ht="30.0" customHeight="1">
-      <c r="A15" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="33" t="s">
+      <c r="B15" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="33" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36" t="s">
+      <c r="L15" s="37"/>
+      <c r="M15" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="P15" s="33" t="s">
+      <c r="N15" s="37"/>
+      <c r="O15" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="38"/>
+      <c r="P15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="41"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="40" t="s">
+      <c r="A16" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="43" t="s">
+      <c r="B16" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="44"/>
-      <c r="M16" s="43" t="s">
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="N16" s="44"/>
-      <c r="O16" s="45" t="s">
+      <c r="L16" s="47"/>
+      <c r="M16" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="P16" s="46" t="s">
+      <c r="N16" s="47"/>
+      <c r="O16" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="38"/>
+      <c r="P16" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="41"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="50" t="s">
+      <c r="A17" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="38"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="41"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="52" t="s">
-        <v>34</v>
+      <c r="A18" s="55" t="s">
+        <v>35</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1315,15 +1332,15 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="38"/>
+      <c r="P18" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="41"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1339,15 +1356,15 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q19" s="54"/>
-      <c r="R19" s="38"/>
+      <c r="P19" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="41"/>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>38</v>
+      <c r="A20" s="32" t="s">
+        <v>39</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1367,8 +1384,8 @@
       <c r="Q20" s="3"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="56" t="s">
-        <v>39</v>
+      <c r="A21" s="58" t="s">
+        <v>40</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -1387,41 +1404,41 @@
       <c r="P21" s="29"/>
       <c r="Q21" s="29"/>
     </row>
-    <row r="22" ht="3.0" customHeight="1">
+    <row r="22" ht="60.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
+      <c r="D22" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="33"/>
       <c r="Q22" s="1"/>
     </row>
     <row r="23" ht="27.75" customHeight="1">
-      <c r="A23" s="57" t="s">
-        <v>40</v>
+      <c r="A23" s="60" t="s">
+        <v>42</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="58" t="s">
-        <v>41</v>
-      </c>
+      <c r="F23" s="61"/>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="57" t="s">
-        <v>13</v>
+      <c r="J23" s="62" t="s">
+        <v>43</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
@@ -1451,21 +1468,19 @@
       <c r="Q24" s="1"/>
     </row>
     <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="57" t="s">
-        <v>42</v>
+      <c r="A25" s="60" t="s">
+        <v>44</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="58" t="s">
-        <v>43</v>
-      </c>
+      <c r="F25" s="61"/>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="57" t="s">
-        <v>13</v>
+      <c r="J25" s="62" t="s">
+        <v>45</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
@@ -2451,7 +2466,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="42">
     <mergeCell ref="D1:P1"/>
     <mergeCell ref="A2:K3"/>
     <mergeCell ref="L2:M2"/>
@@ -2464,6 +2479,7 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="H5:K5"/>
     <mergeCell ref="L5:M5"/>
@@ -2473,11 +2489,13 @@
     <mergeCell ref="A9:Q9"/>
     <mergeCell ref="E11:Q11"/>
     <mergeCell ref="E13:Q13"/>
+    <mergeCell ref="E14:Q14"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="D22:P22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="J23:Q23"/>
@@ -2485,12 +2503,12 @@
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="J25:Q25"/>
     <mergeCell ref="A17:O17"/>
+    <mergeCell ref="P17:Q17"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="P18:Q18"/>
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="A20:Q20"/>
-    <mergeCell ref="A21:Q21"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/app/templates/schet-shablon.xlsx
+++ b/app/templates/schet-shablon.xlsx
@@ -204,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="44">
     <border/>
     <border>
       <left/>
@@ -401,11 +401,6 @@
       </bottom>
     </border>
     <border>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -545,12 +540,25 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -611,29 +619,22 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="28" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="29" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="30" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="32" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="32" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="30" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="33" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="35" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="36" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="33" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="34" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="35" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -651,44 +652,50 @@
     <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="37" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="36" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="38" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="39" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="37" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="38" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="39" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="20" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="41" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="26" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="41" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="42" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="41" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="43" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1204,13 +1211,13 @@
       <c r="Q13" s="3"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="30" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="31" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="3"/>
@@ -1224,98 +1231,98 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="33"/>
+      <c r="Q14" s="3"/>
     </row>
     <row r="15" ht="30.0" customHeight="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="38" t="s">
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="37"/>
-      <c r="M15" s="35" t="s">
+      <c r="L15" s="35"/>
+      <c r="M15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="37"/>
-      <c r="O15" s="39" t="s">
+      <c r="N15" s="35"/>
+      <c r="O15" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="P15" s="35" t="s">
+      <c r="P15" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="41"/>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="38"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="46" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="47"/>
-      <c r="M16" s="46" t="s">
+      <c r="L16" s="44"/>
+      <c r="M16" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="N16" s="47"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="44"/>
+      <c r="O16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="P16" s="49" t="s">
+      <c r="P16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="41"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="38"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="53" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="41"/>
+      <c r="Q17" s="51"/>
+      <c r="R17" s="38"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="52" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="3"/>
@@ -1332,14 +1339,14 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="56" t="s">
+      <c r="P18" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="41"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="38"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="52" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="3"/>
@@ -1356,14 +1363,14 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="56" t="s">
+      <c r="P19" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="41"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="38"/>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="30" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="3"/>
@@ -1384,7 +1391,7 @@
       <c r="Q20" s="3"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="54" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="29"/>
@@ -1404,11 +1411,11 @@
       <c r="P21" s="29"/>
       <c r="Q21" s="29"/>
     </row>
-    <row r="22" ht="60.75" customHeight="1">
+    <row r="22" ht="73.5" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="55" t="s">
         <v>41</v>
       </c>
       <c r="E22" s="3"/>
@@ -1422,31 +1429,31 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="33"/>
+      <c r="P22" s="3"/>
       <c r="Q22" s="1"/>
     </row>
     <row r="23" ht="27.75" customHeight="1">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="56" t="s">
         <v>42</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="61"/>
+      <c r="F23" s="57"/>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="62" t="s">
+      <c r="I23" s="58"/>
+      <c r="J23" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
       <c r="A24" s="1"/>
@@ -1457,38 +1464,38 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
     <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="56" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="61"/>
+      <c r="F25" s="57"/>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="62" t="s">
+      <c r="I25" s="58"/>
+      <c r="J25" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
     </row>
     <row r="26" ht="12.75" customHeight="1"/>
     <row r="27" ht="12.75" customHeight="1"/>
@@ -2466,7 +2473,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="D1:P1"/>
     <mergeCell ref="A2:K3"/>
     <mergeCell ref="L2:M2"/>
@@ -2494,14 +2501,7 @@
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="A21:Q21"/>
-    <mergeCell ref="D22:P22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:Q23"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="J25:Q25"/>
+    <mergeCell ref="P16:Q16"/>
     <mergeCell ref="A17:O17"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="A18:O18"/>
@@ -2509,6 +2509,14 @@
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="A20:Q20"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="D22:P22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="J23:O23"/>
+    <mergeCell ref="J25:O25"/>
+    <mergeCell ref="F25:H25"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/app/templates/schet-shablon.xlsx
+++ b/app/templates/schet-shablon.xlsx
@@ -136,19 +136,19 @@
     <t>{{total_sum_text}}</t>
   </si>
   <si>
+    <t>Руководитель</t>
+  </si>
+  <si>
+    <t>{{director_name}}</t>
+  </si>
+  <si>
+    <t>Главный бухгалтер</t>
+  </si>
+  <si>
+    <t>{{accountant_name}}</t>
+  </si>
+  <si>
     <t>{{head_warning}}</t>
-  </si>
-  <si>
-    <t>Руководитель</t>
-  </si>
-  <si>
-    <t>{{director_name}}</t>
-  </si>
-  <si>
-    <t>Главный бухгалтер</t>
-  </si>
-  <si>
-    <t>{{accountant_name}}</t>
   </si>
 </sst>
 </file>
@@ -558,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -675,9 +675,6 @@
     </xf>
     <xf borderId="26" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -1411,93 +1408,93 @@
       <c r="P21" s="29"/>
       <c r="Q21" s="29"/>
     </row>
-    <row r="22" ht="73.5" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="55" t="s">
+    <row r="22" ht="27.75" customHeight="1">
+      <c r="A22" s="55" t="s">
         <v>41</v>
       </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="1"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="59"/>
     </row>
-    <row r="23" ht="27.75" customHeight="1">
-      <c r="A23" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="59" t="s">
+    <row r="23" ht="10.5" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" ht="27.75" customHeight="1">
+      <c r="A24" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="59"/>
     </row>
-    <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+    <row r="25" ht="28.5" customHeight="1"/>
+    <row r="26" ht="192.0" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="1"/>
     </row>
-    <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59" t="s">
-        <v>45</v>
-      </c>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-    </row>
-    <row r="26" ht="12.75" customHeight="1"/>
     <row r="27" ht="12.75" customHeight="1"/>
     <row r="28" ht="12.75" customHeight="1"/>
     <row r="29" ht="12.75" customHeight="1"/>
@@ -2508,15 +2505,15 @@
     <mergeCell ref="P18:Q18"/>
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="D26:P26"/>
     <mergeCell ref="A20:Q20"/>
     <mergeCell ref="A21:Q21"/>
-    <mergeCell ref="D22:P22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="J23:O23"/>
-    <mergeCell ref="J25:O25"/>
-    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/app/templates/schet-shablon.xlsx
+++ b/app/templates/schet-shablon.xlsx
@@ -136,6 +136,9 @@
     <t>{{total_sum_text}}</t>
   </si>
   <si>
+    <t>{{head_warning}}</t>
+  </si>
+  <si>
     <t>Руководитель</t>
   </si>
   <si>
@@ -146,9 +149,6 @@
   </si>
   <si>
     <t>{{accountant_name}}</t>
-  </si>
-  <si>
-    <t>{{head_warning}}</t>
   </si>
 </sst>
 </file>
@@ -204,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="45">
     <border/>
     <border>
       <left/>
@@ -537,6 +537,10 @@
     <border>
       <left/>
       <top/>
+    </border>
+    <border>
+      <left/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -558,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -676,22 +680,31 @@
     <xf borderId="26" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="41" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="41" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="41" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="42" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="42" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="43" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="41" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="42" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="43" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="44" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1408,94 +1421,112 @@
       <c r="P21" s="29"/>
       <c r="Q21" s="29"/>
     </row>
-    <row r="22" ht="27.75" customHeight="1">
-      <c r="A22" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+    <row r="22">
+      <c r="A22" s="55"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
       <c r="F22" s="56"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="55"/>
     </row>
-    <row r="23" ht="10.5" customHeight="1">
+    <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="1"/>
+      <c r="D23" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
       <c r="Q23" s="1"/>
     </row>
     <row r="24" ht="27.75" customHeight="1">
-      <c r="A24" s="55" t="s">
-        <v>43</v>
+      <c r="A24" s="58" t="s">
+        <v>42</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="56"/>
+      <c r="F24" s="59"/>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="58" t="s">
-        <v>44</v>
+      <c r="I24" s="60"/>
+      <c r="J24" s="61" t="s">
+        <v>43</v>
       </c>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="59"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
     </row>
-    <row r="25" ht="28.5" customHeight="1"/>
-    <row r="26" ht="192.0" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="2" t="s">
+    <row r="25" ht="10.5" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="63"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" ht="27.75" customHeight="1">
+      <c r="A26" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="1"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
     </row>
-    <row r="27" ht="12.75" customHeight="1"/>
+    <row r="27" ht="28.5" customHeight="1"/>
     <row r="28" ht="12.75" customHeight="1"/>
     <row r="29" ht="12.75" customHeight="1"/>
     <row r="30" ht="12.75" customHeight="1"/>
@@ -1694,7 +1725,7 @@
     <row r="223" ht="12.75" customHeight="1"/>
     <row r="224" ht="12.75" customHeight="1"/>
     <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
     <row r="228" ht="15.75" customHeight="1"/>
     <row r="229" ht="15.75" customHeight="1"/>
@@ -2469,6 +2500,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
     <mergeCell ref="D1:P1"/>
@@ -2505,15 +2537,15 @@
     <mergeCell ref="P18:Q18"/>
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="J24:O24"/>
-    <mergeCell ref="D26:P26"/>
     <mergeCell ref="A20:Q20"/>
     <mergeCell ref="A21:Q21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:O22"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="F24:H24"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D23:P23"/>
+    <mergeCell ref="J26:O26"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
